--- a/sampleprojects/TaxReturn/excel/states/IL.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/IL.xlsx
@@ -71,7 +71,7 @@
     <t>IL exemptions = $2,850 x (taxpayers + dependents); tax = 4.95% x max(AGI - exemptions, 0)</t>
   </si>
   <si>
-    <t>set result.il_total_exemptions = (length of job.taxpayers + length of job.dependents) * il_personal_exemption; set result.il_taxable_income = the maximum of (result.agi - result.il_total_exemptions) and 0.0; set result.il_state_tax = result.il_taxable_income * il_tax_rate; add "  IL exemptions ($2,850 per person): $" + result.il_total_exemptions to job.audit_trail; add "  IL state tax (4.95%): $" + result.il_state_tax to job.audit_trail</t>
+    <t>set result.il_total_exemptions = (length of job.taxpayers + length of job.dependents) * il_personal_exemption; set result.il_taxable_income = the maximum of (result.state_calc_agi - result.il_total_exemptions) and 0.0; set result.il_state_tax = result.il_taxable_income * il_tax_rate; add "  IL exemptions ($2,850 per person): $" + result.il_total_exemptions to job.audit_trail; add "  IL state tax (4.95%): $" + result.il_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>

--- a/sampleprojects/TaxReturn/excel/states/IL.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/IL.xlsx
@@ -44,7 +44,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.il_state_tax = 0; set result.il_taxable_income = 0; set result.il_total_exemptions = 0; add "  Illinois Tax Calculation (Form IL-1040) - flat 4.95%" to job.audit_trail</t>
+    <t>set result.il_state_tax = 0; set result.il_taxable_income = 0; set result.il_total_exemptions = 0; add "  Illinois Tax Calculation (Form IL-1040) - flat 4.95%" to job.audit_trail; set result.il_military_retirement_exclusion = result.military_retirement_income; set result.il_adjusted_agi = the maximum of (result.state_calc_agi - result.il_military_retirement_exclusion) and 0.0; add "  IL-1040 line 5 retirement subtraction (military retired pay): $" + result.il_military_retirement_exclusion to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -68,10 +68,10 @@
     <t>DSL: ACTIONS</t>
   </si>
   <si>
-    <t>IL exemptions = $2,850 x (taxpayers + dependents); tax = 4.95% x max(AGI - exemptions, 0)</t>
-  </si>
-  <si>
-    <t>set result.il_total_exemptions = (length of job.taxpayers + length of job.dependents) * il_personal_exemption; set result.il_taxable_income = the maximum of (result.state_calc_agi - result.il_total_exemptions) and 0.0; set result.il_state_tax = result.il_taxable_income * il_tax_rate; add "  IL exemptions ($2,850 per person): $" + result.il_total_exemptions to job.audit_trail; add "  IL state tax (4.95%): $" + result.il_state_tax to job.audit_trail</t>
+    <t>IL-1040: base income (line 9) is federal AGI less the line 5 retirement subtraction; exemptions $2,850 per person (line 10); tax 4.95% (line 12)</t>
+  </si>
+  <si>
+    <t>set result.il_total_exemptions = (length of job.taxpayers + length of job.dependents) * il_personal_exemption; set result.il_taxable_income = the maximum of (result.il_adjusted_agi - result.il_total_exemptions) and 0.0; set result.il_state_tax = result.il_taxable_income * il_tax_rate; add "  IL exemptions ($2,850 per person): $" + result.il_total_exemptions to job.audit_trail; add "  IL state tax (4.95%): $" + result.il_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>
@@ -89,7 +89,7 @@
     <t>Policy Statements</t>
   </si>
   <si>
-    <t>IL flat tax: 4.95% x max(AGI - $2,850 x #people, 0)</t>
+    <t>Illinois flat 4.95% on federal AGI less the IL-1040 line 5 subtraction of federally taxed retirement income, which includes military retired pay in full (2025 IL-1040 instructions; Pub. 120; 35 ILCS 5/203(a)(2)(F)), less $2,850 per exemption.</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -158,7 +158,7 @@
     <t>il_military_retirement_exclusion</t>
   </si>
   <si>
-    <t>Illinois military retirement exclusion amount (computed). 100% of military retirement pay is exempt from Illinois income tax per 35 ILCS 5/203(a)(2)(K). No age limits, no dollar caps. MOAA State Report Card: Grade A. Source: https://turbotax.intuit.com/tax-tips/military/states-that-dont-tax-military-retirement/</t>
+    <t>Illinois subtraction of military retired pay (computed per return in il_tax): retirement income taxed federally, including government retirement plans and military plans, is subtracted in full on IL-1040 line 5 (2025 IL-1040 instructions; Publication 120; 35 ILCS 5/203(a)(2)(F)). No age limit or cap (#1330).</t>
   </si>
   <si>
     <t>il_msrra_compliant</t>

--- a/sampleprojects/TaxReturn/excel/states/IL.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/IL.xlsx
@@ -44,7 +44,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.il_state_tax = 0; set result.il_taxable_income = 0; set result.il_total_exemptions = 0; add "  Illinois Tax Calculation (Form IL-1040) - flat 4.95%" to job.audit_trail; set result.il_military_retirement_exclusion = result.military_retirement_income; set result.il_adjusted_agi = the maximum of (result.state_calc_agi - result.il_military_retirement_exclusion) and 0.0; add "  IL-1040 line 5 retirement subtraction (military retired pay): $" + result.il_military_retirement_exclusion to job.audit_trail</t>
+    <t>set result.il_state_tax = 0; set result.il_taxable_income = 0; set result.il_total_exemptions = 0; add "  Illinois Tax Calculation (Form IL-1040) - flat 4.95%" to job.audit_trail; set result.il_military_retirement_exclusion = 0.0; if result.state_calc_resident_status is equal to "full_year" then { set result.il_military_retirement_exclusion = result.military_retirement_income; } endif; set result.il_adjusted_agi = the maximum of (result.state_calc_agi - result.il_military_retirement_exclusion) and 0.0; add "  IL-1040 line 5 retirement subtraction (military retired pay): $" + result.il_military_retirement_exclusion to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>

--- a/sampleprojects/TaxReturn/excel/states/IL.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/IL.xlsx
@@ -44,7 +44,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.il_state_tax = 0; set result.il_taxable_income = 0; set result.il_total_exemptions = 0; add "  Illinois Tax Calculation (Form IL-1040) - flat 4.95%" to job.audit_trail</t>
+    <t>set result.il_state_tax = 0; set result.il_taxable_income = 0; set result.il_total_exemptions = 0; add "  Illinois Tax Calculation (Form IL-1040) - flat 4.95%" to job.audit_trail; set result.il_military_retirement_exclusion = 0.0; if result.state_calc_resident_status is equal to "full_year" then { set result.il_military_retirement_exclusion = result.military_retirement_income; } endif; set result.il_adjusted_agi = the maximum of (result.state_calc_agi - result.il_military_retirement_exclusion) and 0.0; add "  IL-1040 line 5 retirement subtraction (military retired pay): $" + result.il_military_retirement_exclusion to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -68,10 +68,10 @@
     <t>DSL: ACTIONS</t>
   </si>
   <si>
-    <t>IL exemptions = $2,850 x (taxpayers + dependents); tax = 4.95% x max(AGI - exemptions, 0)</t>
-  </si>
-  <si>
-    <t>set result.il_total_exemptions = (length of job.taxpayers + length of job.dependents) * il_personal_exemption; set result.il_taxable_income = the maximum of (result.state_calc_agi - result.il_total_exemptions) and 0.0; set result.il_state_tax = result.il_taxable_income * il_tax_rate; add "  IL exemptions ($2,850 per person): $" + result.il_total_exemptions to job.audit_trail; add "  IL state tax (4.95%): $" + result.il_state_tax to job.audit_trail</t>
+    <t>IL-1040: base income (line 9) is federal AGI less the line 5 retirement subtraction; exemptions $2,850 per person (line 10); tax 4.95% (line 12)</t>
+  </si>
+  <si>
+    <t>set result.il_total_exemptions = (length of job.taxpayers + length of job.dependents) * il_personal_exemption; set result.il_taxable_income = the maximum of (result.il_adjusted_agi - result.il_total_exemptions) and 0.0; set result.il_state_tax = result.il_taxable_income * il_tax_rate; add "  IL exemptions ($2,850 per person): $" + result.il_total_exemptions to job.audit_trail; add "  IL state tax (4.95%): $" + result.il_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>
@@ -89,7 +89,7 @@
     <t>Policy Statements</t>
   </si>
   <si>
-    <t>IL flat tax: 4.95% x max(AGI - $2,850 x #people, 0)</t>
+    <t>Illinois flat 4.95% on federal AGI less the IL-1040 line 5 subtraction of federally taxed retirement income, which includes military retired pay in full (2025 IL-1040 instructions; Pub. 120; 35 ILCS 5/203(a)(2)(F)), less $2,850 per exemption.</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -158,7 +158,7 @@
     <t>il_military_retirement_exclusion</t>
   </si>
   <si>
-    <t>Illinois military retirement exclusion amount (computed). 100% of military retirement pay is exempt from Illinois income tax per 35 ILCS 5/203(a)(2)(K). No age limits, no dollar caps. MOAA State Report Card: Grade A. Source: https://turbotax.intuit.com/tax-tips/military/states-that-dont-tax-military-retirement/</t>
+    <t>Illinois subtraction of military retired pay (computed per return in il_tax): retirement income taxed federally, including government retirement plans and military plans, is subtracted in full on IL-1040 line 5 (2025 IL-1040 instructions; Publication 120; 35 ILCS 5/203(a)(2)(F)). No age limit or cap (#1330).</t>
   </si>
   <si>
     <t>il_msrra_compliant</t>
